--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Texas-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7288EBC-EE13-4886-BF0E-A2D615E3D374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6779C6FA-3F7B-44C0-B12C-7CB108A2D431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16474,7 +16474,7 @@
         <v>46176.426041666666</v>
       </c>
       <c r="J568">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K568" t="s">
         <v>11</v>
@@ -16503,7 +16503,7 @@
         <v>46176.426041666666</v>
       </c>
       <c r="J569">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K569" t="s">
         <v>11</v>
@@ -16532,7 +16532,7 @@
         <v>46176.426736111112</v>
       </c>
       <c r="J570">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K570" t="s">
         <v>11</v>
@@ -16561,7 +16561,7 @@
         <v>46176.426736111112</v>
       </c>
       <c r="J571">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K571" t="s">
         <v>11</v>
@@ -16590,7 +16590,7 @@
         <v>46176.427430555559</v>
       </c>
       <c r="J572">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K572" t="s">
         <v>11</v>
@@ -16619,7 +16619,7 @@
         <v>46176.427430555559</v>
       </c>
       <c r="J573">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K573" t="s">
         <v>11</v>
@@ -16648,7 +16648,7 @@
         <v>46176.428124999999</v>
       </c>
       <c r="J574">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K574" t="s">
         <v>11</v>
@@ -16677,7 +16677,7 @@
         <v>46176.428124999999</v>
       </c>
       <c r="J575">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K575" t="s">
         <v>11</v>
@@ -16735,7 +16735,7 @@
         <v>46176.428819444445</v>
       </c>
       <c r="J577">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K577" t="s">
         <v>11</v>
@@ -16764,7 +16764,7 @@
         <v>46176.428819444445</v>
       </c>
       <c r="J578">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K578" t="s">
         <v>11</v>
@@ -16793,7 +16793,7 @@
         <v>46176.428819444445</v>
       </c>
       <c r="J579">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K579" t="s">
         <v>11</v>
@@ -16851,7 +16851,7 @@
         <v>46176.429513888892</v>
       </c>
       <c r="J581">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K581" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Texas-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FB1EE90-81C7-495F-B927-B037765614B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05BFA9D8-5A35-4265-8F11-1341A37EB300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2989" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2988" uniqueCount="75">
   <si>
     <t>Company Name</t>
   </si>
@@ -146,13 +146,7 @@
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>DNU-Speed Management</t>
-  </si>
-  <si>
-    <t>DNU-Def.Drive Distracted Driving</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>Safe RR Crossing</t>
   </si>
   <si>
     <t>3 points of contact</t>
@@ -161,10 +155,16 @@
     <t>Vehicle &amp; Roadside Inspections CMV</t>
   </si>
   <si>
-    <t>Safe RR Crossing</t>
+    <t>DNU-Def.Drive Distracted Driving</t>
+  </si>
+  <si>
+    <t>DNU-Speed Management</t>
   </si>
   <si>
     <t>DNUNEW-Space Management Big 5</t>
+  </si>
+  <si>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Texas Towing Wrecker Service</t>
@@ -637,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -713,7 +713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>42</v>
       </c>
@@ -887,7 +887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>42</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>42</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
@@ -1380,7 +1380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>42</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
@@ -1449,7 +1449,7 @@
         <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G28" t="s">
         <v>10</v>
@@ -1478,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
@@ -1507,7 +1507,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G30" t="s">
         <v>10</v>
@@ -1536,7 +1536,7 @@
         <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -1554,7 +1554,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>42</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>50</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -1594,7 +1594,7 @@
         <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -1631,7 +1631,7 @@
         <v>52</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -1660,7 +1660,7 @@
         <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
@@ -1689,7 +1689,7 @@
         <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
@@ -1718,7 +1718,7 @@
         <v>55</v>
       </c>
       <c r="F38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G38" t="s">
         <v>13</v>
@@ -1747,7 +1747,7 @@
         <v>56</v>
       </c>
       <c r="F39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G39" t="s">
         <v>14</v>
@@ -1784,7 +1784,7 @@
         <v>57</v>
       </c>
       <c r="F41" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -1802,7 +1802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H42" s="2"/>
       <c r="I42" s="1"/>
       <c r="J42" s="2"/>
@@ -1821,7 +1821,7 @@
         <v>58</v>
       </c>
       <c r="F43" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G43" t="s">
         <v>10</v>
@@ -1850,7 +1850,7 @@
         <v>59</v>
       </c>
       <c r="F44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -1879,7 +1879,7 @@
         <v>60</v>
       </c>
       <c r="F45" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G45" t="s">
         <v>10</v>
@@ -1908,7 +1908,7 @@
         <v>61</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G46" t="s">
         <v>10</v>
@@ -1937,7 +1937,7 @@
         <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G47" t="s">
         <v>13</v>
@@ -1966,7 +1966,7 @@
         <v>63</v>
       </c>
       <c r="F48" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
@@ -2003,7 +2003,7 @@
         <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G50" t="s">
         <v>10</v>
@@ -2032,7 +2032,7 @@
         <v>65</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>43</v>
       </c>
       <c r="F52" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -2090,7 +2090,7 @@
         <v>44</v>
       </c>
       <c r="F53" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -2108,7 +2108,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>42</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>45</v>
       </c>
       <c r="F54" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G54" t="s">
         <v>13</v>
@@ -2148,7 +2148,7 @@
         <v>46</v>
       </c>
       <c r="F55" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2177,7 +2177,7 @@
         <v>47</v>
       </c>
       <c r="F56" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G56" t="s">
         <v>13</v>
@@ -2206,7 +2206,7 @@
         <v>48</v>
       </c>
       <c r="F57" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G57" t="s">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G58" t="s">
         <v>13</v>
@@ -2264,7 +2264,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
@@ -2293,7 +2293,7 @@
         <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G60" t="s">
         <v>13</v>
@@ -2322,7 +2322,7 @@
         <v>52</v>
       </c>
       <c r="F61" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
@@ -2351,7 +2351,7 @@
         <v>53</v>
       </c>
       <c r="F62" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
@@ -2380,7 +2380,7 @@
         <v>54</v>
       </c>
       <c r="F63" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G63" t="s">
         <v>13</v>
@@ -2409,7 +2409,7 @@
         <v>55</v>
       </c>
       <c r="F64" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G64" t="s">
         <v>10</v>
@@ -2438,7 +2438,7 @@
         <v>56</v>
       </c>
       <c r="F65" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G65" t="s">
         <v>10</v>
@@ -2467,7 +2467,7 @@
         <v>57</v>
       </c>
       <c r="F66" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2496,7 +2496,7 @@
         <v>58</v>
       </c>
       <c r="F67" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2525,7 +2525,7 @@
         <v>59</v>
       </c>
       <c r="F68" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G68" t="s">
         <v>13</v>
@@ -2554,7 +2554,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G69" t="s">
         <v>10</v>
@@ -2583,7 +2583,7 @@
         <v>61</v>
       </c>
       <c r="F70" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G70" t="s">
         <v>10</v>
@@ -2612,7 +2612,7 @@
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2641,7 +2641,7 @@
         <v>63</v>
       </c>
       <c r="F72" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G72" t="s">
         <v>10</v>
@@ -2670,7 +2670,7 @@
         <v>64</v>
       </c>
       <c r="F73" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2688,7 +2688,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>42</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>65</v>
       </c>
       <c r="F74" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>43</v>
       </c>
       <c r="F75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -2757,7 +2757,7 @@
         <v>44</v>
       </c>
       <c r="F76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G76" t="s">
         <v>10</v>
@@ -2786,7 +2786,7 @@
         <v>46</v>
       </c>
       <c r="F77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G77" t="s">
         <v>13</v>
@@ -2815,7 +2815,7 @@
         <v>47</v>
       </c>
       <c r="F78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G78" t="s">
         <v>13</v>
@@ -2844,7 +2844,7 @@
         <v>48</v>
       </c>
       <c r="F79" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G79" t="s">
         <v>10</v>
@@ -2873,7 +2873,7 @@
         <v>49</v>
       </c>
       <c r="F80" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G80" t="s">
         <v>13</v>
@@ -2902,7 +2902,7 @@
         <v>50</v>
       </c>
       <c r="F81" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G81" t="s">
         <v>13</v>
@@ -2920,7 +2920,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>42</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>51</v>
       </c>
       <c r="F82" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G82" t="s">
         <v>13</v>
@@ -2960,7 +2960,7 @@
         <v>52</v>
       </c>
       <c r="F83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G83" t="s">
         <v>13</v>
@@ -2989,7 +2989,7 @@
         <v>53</v>
       </c>
       <c r="F84" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G84" t="s">
         <v>13</v>
@@ -3018,7 +3018,7 @@
         <v>54</v>
       </c>
       <c r="F85" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G85" t="s">
         <v>13</v>
@@ -3047,7 +3047,7 @@
         <v>55</v>
       </c>
       <c r="F86" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G86" t="s">
         <v>10</v>
@@ -3076,7 +3076,7 @@
         <v>56</v>
       </c>
       <c r="F87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G87" t="s">
         <v>14</v>
@@ -3113,7 +3113,7 @@
         <v>57</v>
       </c>
       <c r="F89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G89" t="s">
         <v>14</v>
@@ -3150,7 +3150,7 @@
         <v>58</v>
       </c>
       <c r="F91" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G91" t="s">
         <v>13</v>
@@ -3168,7 +3168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>42</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>59</v>
       </c>
       <c r="F92" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G92" t="s">
         <v>13</v>
@@ -3208,7 +3208,7 @@
         <v>60</v>
       </c>
       <c r="F93" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G93" t="s">
         <v>10</v>
@@ -3237,7 +3237,7 @@
         <v>61</v>
       </c>
       <c r="F94" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G94" t="s">
         <v>12</v>
@@ -3274,7 +3274,7 @@
         <v>62</v>
       </c>
       <c r="F96" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G96" t="s">
         <v>13</v>
@@ -3303,7 +3303,7 @@
         <v>63</v>
       </c>
       <c r="F97" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G97" t="s">
         <v>13</v>
@@ -3332,7 +3332,7 @@
         <v>64</v>
       </c>
       <c r="F98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G98" t="s">
         <v>13</v>
@@ -3361,7 +3361,7 @@
         <v>65</v>
       </c>
       <c r="F99" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G99" t="s">
         <v>10</v>
@@ -3706,7 +3706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>42</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>42</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>42</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>42</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>42</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>42</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>42</v>
       </c>
@@ -6417,7 +6417,7 @@
         <v>43</v>
       </c>
       <c r="F208" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G208" t="s">
         <v>13</v>
@@ -6446,7 +6446,7 @@
         <v>44</v>
       </c>
       <c r="F209" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G209" t="s">
         <v>10</v>
@@ -6475,7 +6475,7 @@
         <v>66</v>
       </c>
       <c r="F210" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G210" t="s">
         <v>10</v>
@@ -6504,7 +6504,7 @@
         <v>46</v>
       </c>
       <c r="F211" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G211" t="s">
         <v>13</v>
@@ -6533,7 +6533,7 @@
         <v>47</v>
       </c>
       <c r="F212" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G212" t="s">
         <v>13</v>
@@ -6562,7 +6562,7 @@
         <v>48</v>
       </c>
       <c r="F213" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G213" t="s">
         <v>10</v>
@@ -6591,7 +6591,7 @@
         <v>49</v>
       </c>
       <c r="F214" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G214" t="s">
         <v>13</v>
@@ -6620,7 +6620,7 @@
         <v>50</v>
       </c>
       <c r="F215" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G215" t="s">
         <v>13</v>
@@ -6649,7 +6649,7 @@
         <v>52</v>
       </c>
       <c r="F216" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G216" t="s">
         <v>13</v>
@@ -6678,7 +6678,7 @@
         <v>56</v>
       </c>
       <c r="F217" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G217" t="s">
         <v>14</v>
@@ -6715,7 +6715,7 @@
         <v>57</v>
       </c>
       <c r="F219" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G219" t="s">
         <v>10</v>
@@ -6744,7 +6744,7 @@
         <v>58</v>
       </c>
       <c r="F220" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G220" t="s">
         <v>13</v>
@@ -6773,7 +6773,7 @@
         <v>59</v>
       </c>
       <c r="F221" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G221" t="s">
         <v>13</v>
@@ -6802,7 +6802,7 @@
         <v>60</v>
       </c>
       <c r="F222" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G222" t="s">
         <v>10</v>
@@ -6831,7 +6831,7 @@
         <v>61</v>
       </c>
       <c r="F223" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G223" t="s">
         <v>10</v>
@@ -6860,7 +6860,7 @@
         <v>62</v>
       </c>
       <c r="F224" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G224" t="s">
         <v>13</v>
@@ -6889,7 +6889,7 @@
         <v>67</v>
       </c>
       <c r="F225" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G225" t="s">
         <v>10</v>
@@ -6918,7 +6918,7 @@
         <v>63</v>
       </c>
       <c r="F226" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G226" t="s">
         <v>10</v>
@@ -6947,7 +6947,7 @@
         <v>64</v>
       </c>
       <c r="F227" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G227" t="s">
         <v>10</v>
@@ -6976,7 +6976,7 @@
         <v>65</v>
       </c>
       <c r="F228" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G228" t="s">
         <v>10</v>
@@ -7005,7 +7005,7 @@
         <v>43</v>
       </c>
       <c r="F229" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G229" t="s">
         <v>10</v>
@@ -7034,7 +7034,7 @@
         <v>44</v>
       </c>
       <c r="F230" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G230" t="s">
         <v>10</v>
@@ -7063,7 +7063,7 @@
         <v>66</v>
       </c>
       <c r="F231" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G231" t="s">
         <v>13</v>
@@ -7092,7 +7092,7 @@
         <v>46</v>
       </c>
       <c r="F232" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G232" t="s">
         <v>13</v>
@@ -7121,7 +7121,7 @@
         <v>47</v>
       </c>
       <c r="F233" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G233" t="s">
         <v>13</v>
@@ -7150,7 +7150,7 @@
         <v>48</v>
       </c>
       <c r="F234" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G234" t="s">
         <v>10</v>
@@ -7179,7 +7179,7 @@
         <v>49</v>
       </c>
       <c r="F235" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G235" t="s">
         <v>13</v>
@@ -7208,7 +7208,7 @@
         <v>50</v>
       </c>
       <c r="F236" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G236" t="s">
         <v>13</v>
@@ -7237,7 +7237,7 @@
         <v>52</v>
       </c>
       <c r="F237" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G237" t="s">
         <v>13</v>
@@ -7266,7 +7266,7 @@
         <v>56</v>
       </c>
       <c r="F238" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G238" t="s">
         <v>14</v>
@@ -7284,7 +7284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -7303,7 +7303,7 @@
         <v>57</v>
       </c>
       <c r="F240" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G240" t="s">
         <v>10</v>
@@ -7332,7 +7332,7 @@
         <v>58</v>
       </c>
       <c r="F241" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G241" t="s">
         <v>13</v>
@@ -7361,7 +7361,7 @@
         <v>59</v>
       </c>
       <c r="F242" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G242" t="s">
         <v>13</v>
@@ -7390,7 +7390,7 @@
         <v>60</v>
       </c>
       <c r="F243" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G243" t="s">
         <v>13</v>
@@ -7419,7 +7419,7 @@
         <v>61</v>
       </c>
       <c r="F244" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G244" t="s">
         <v>13</v>
@@ -7448,7 +7448,7 @@
         <v>62</v>
       </c>
       <c r="F245" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G245" t="s">
         <v>13</v>
@@ -7477,7 +7477,7 @@
         <v>67</v>
       </c>
       <c r="F246" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G246" t="s">
         <v>10</v>
@@ -7506,7 +7506,7 @@
         <v>63</v>
       </c>
       <c r="F247" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G247" t="s">
         <v>10</v>
@@ -7535,7 +7535,7 @@
         <v>64</v>
       </c>
       <c r="F248" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G248" t="s">
         <v>12</v>
@@ -7572,7 +7572,7 @@
         <v>65</v>
       </c>
       <c r="F250" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G250" t="s">
         <v>10</v>
@@ -8239,7 +8239,7 @@
         <v>43</v>
       </c>
       <c r="F273" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G273" t="s">
         <v>10</v>
@@ -8268,7 +8268,7 @@
         <v>44</v>
       </c>
       <c r="F274" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G274" t="s">
         <v>10</v>
@@ -8297,7 +8297,7 @@
         <v>66</v>
       </c>
       <c r="F275" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G275" t="s">
         <v>10</v>
@@ -8326,7 +8326,7 @@
         <v>46</v>
       </c>
       <c r="F276" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G276" t="s">
         <v>10</v>
@@ -8355,7 +8355,7 @@
         <v>47</v>
       </c>
       <c r="F277" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G277" t="s">
         <v>10</v>
@@ -8384,7 +8384,7 @@
         <v>48</v>
       </c>
       <c r="F278" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G278" t="s">
         <v>10</v>
@@ -8413,7 +8413,7 @@
         <v>49</v>
       </c>
       <c r="F279" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G279" t="s">
         <v>10</v>
@@ -8442,7 +8442,7 @@
         <v>50</v>
       </c>
       <c r="F280" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G280" t="s">
         <v>13</v>
@@ -8471,7 +8471,7 @@
         <v>52</v>
       </c>
       <c r="F281" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G281" t="s">
         <v>13</v>
@@ -8500,7 +8500,7 @@
         <v>56</v>
       </c>
       <c r="F282" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G282" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>57</v>
       </c>
       <c r="F283" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G283" t="s">
         <v>10</v>
@@ -8558,7 +8558,7 @@
         <v>58</v>
       </c>
       <c r="F284" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G284" t="s">
         <v>10</v>
@@ -8587,7 +8587,7 @@
         <v>59</v>
       </c>
       <c r="F285" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G285" t="s">
         <v>10</v>
@@ -8616,7 +8616,7 @@
         <v>68</v>
       </c>
       <c r="F286" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G286" t="s">
         <v>10</v>
@@ -8645,7 +8645,7 @@
         <v>61</v>
       </c>
       <c r="F287" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G287" t="s">
         <v>10</v>
@@ -8674,7 +8674,7 @@
         <v>62</v>
       </c>
       <c r="F288" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G288" t="s">
         <v>12</v>
@@ -8711,7 +8711,7 @@
         <v>67</v>
       </c>
       <c r="F290" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G290" t="s">
         <v>10</v>
@@ -8740,7 +8740,7 @@
         <v>63</v>
       </c>
       <c r="F291" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G291" t="s">
         <v>10</v>
@@ -8769,7 +8769,7 @@
         <v>64</v>
       </c>
       <c r="F292" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G292" t="s">
         <v>10</v>
@@ -8798,7 +8798,7 @@
         <v>65</v>
       </c>
       <c r="F293" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G293" t="s">
         <v>10</v>
@@ -9673,7 +9673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>42</v>
       </c>
@@ -9992,7 +9992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>42</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>42</v>
       </c>
@@ -10514,7 +10514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>42</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>42</v>
       </c>
@@ -11036,7 +11036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>42</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>42</v>
       </c>
@@ -11804,7 +11804,7 @@
         <v>43</v>
       </c>
       <c r="F401" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G401" t="s">
         <v>10</v>
@@ -11833,7 +11833,7 @@
         <v>44</v>
       </c>
       <c r="F402" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G402" t="s">
         <v>10</v>
@@ -11862,7 +11862,7 @@
         <v>66</v>
       </c>
       <c r="F403" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G403" t="s">
         <v>10</v>
@@ -11891,7 +11891,7 @@
         <v>46</v>
       </c>
       <c r="F404" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G404" t="s">
         <v>13</v>
@@ -11920,7 +11920,7 @@
         <v>47</v>
       </c>
       <c r="F405" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G405" t="s">
         <v>13</v>
@@ -11949,7 +11949,7 @@
         <v>49</v>
       </c>
       <c r="F406" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G406" t="s">
         <v>13</v>
@@ -11978,7 +11978,7 @@
         <v>50</v>
       </c>
       <c r="F407" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G407" t="s">
         <v>13</v>
@@ -12007,7 +12007,7 @@
         <v>52</v>
       </c>
       <c r="F408" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G408" t="s">
         <v>13</v>
@@ -12036,7 +12036,7 @@
         <v>56</v>
       </c>
       <c r="F409" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G409" t="s">
         <v>10</v>
@@ -12065,7 +12065,7 @@
         <v>57</v>
       </c>
       <c r="F410" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G410" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>58</v>
       </c>
       <c r="F411" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G411" t="s">
         <v>13</v>
@@ -12123,7 +12123,7 @@
         <v>59</v>
       </c>
       <c r="F412" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G412" t="s">
         <v>12</v>
@@ -12160,7 +12160,7 @@
         <v>68</v>
       </c>
       <c r="F414" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G414" t="s">
         <v>10</v>
@@ -12189,7 +12189,7 @@
         <v>61</v>
       </c>
       <c r="F415" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G415" t="s">
         <v>10</v>
@@ -12218,7 +12218,7 @@
         <v>62</v>
       </c>
       <c r="F416" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G416" t="s">
         <v>10</v>
@@ -12247,7 +12247,7 @@
         <v>67</v>
       </c>
       <c r="F417" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G417" t="s">
         <v>10</v>
@@ -12276,7 +12276,7 @@
         <v>63</v>
       </c>
       <c r="F418" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G418" t="s">
         <v>10</v>
@@ -12305,7 +12305,7 @@
         <v>64</v>
       </c>
       <c r="F419" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G419" t="s">
         <v>10</v>
@@ -12334,7 +12334,7 @@
         <v>65</v>
       </c>
       <c r="F420" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G420" t="s">
         <v>10</v>
@@ -17898,10 +17898,10 @@
         <v>32</v>
       </c>
       <c r="G619" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H619" s="2">
-        <v>1.1574074074074075E-4</v>
+        <v>5.4629629629629629E-3</v>
       </c>
       <c r="I619" s="1">
         <v>46237.847685185188</v>
@@ -17914,11 +17914,32 @@
       </c>
     </row>
     <row r="620" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H620" s="2"/>
-      <c r="I620" s="1"/>
-      <c r="J620" s="2"/>
+      <c r="B620" t="s">
+        <v>42</v>
+      </c>
+      <c r="C620">
+        <v>834</v>
+      </c>
+      <c r="D620" t="s">
+        <v>63</v>
+      </c>
+      <c r="F620" t="s">
+        <v>32</v>
+      </c>
+      <c r="G620" t="s">
+        <v>10</v>
+      </c>
+      <c r="H620" s="2">
+        <v>6.5509259259259262E-3</v>
+      </c>
+      <c r="I620" s="1">
+        <v>46237.847685185188</v>
+      </c>
+      <c r="J620" s="2">
+        <v>2</v>
+      </c>
       <c r="K620" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="621" spans="2:11" x14ac:dyDescent="0.25">
@@ -17926,10 +17947,10 @@
         <v>42</v>
       </c>
       <c r="C621">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D621" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F621" t="s">
         <v>32</v>
@@ -17938,10 +17959,10 @@
         <v>10</v>
       </c>
       <c r="H621" s="2">
-        <v>6.5509259259259262E-3</v>
+        <v>8.4953703703703701E-3</v>
       </c>
       <c r="I621" s="1">
-        <v>46237.847685185188</v>
+        <v>46237.848379629628</v>
       </c>
       <c r="J621" s="2">
         <v>2</v>
@@ -17955,10 +17976,10 @@
         <v>42</v>
       </c>
       <c r="C622">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="D622" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F622" t="s">
         <v>32</v>
@@ -17967,13 +17988,13 @@
         <v>10</v>
       </c>
       <c r="H622" s="2">
-        <v>8.4953703703703701E-3</v>
+        <v>5.9837962962962961E-3</v>
       </c>
       <c r="I622" s="1">
-        <v>46237.848379629628</v>
+        <v>46237.849074074074</v>
       </c>
       <c r="J622" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K622" s="1" t="s">
         <v>11</v>
@@ -17984,10 +18005,10 @@
         <v>42</v>
       </c>
       <c r="C623">
-        <v>845</v>
+        <v>5230</v>
       </c>
       <c r="D623" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F623" t="s">
         <v>32</v>
@@ -17996,46 +18017,23 @@
         <v>10</v>
       </c>
       <c r="H623" s="2">
-        <v>5.9837962962962961E-3</v>
+        <v>6.828703703703704E-3</v>
       </c>
       <c r="I623" s="1">
         <v>46237.849074074074</v>
       </c>
       <c r="J623" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K623" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="624" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B624" t="s">
-        <v>42</v>
-      </c>
-      <c r="C624">
-        <v>5230</v>
-      </c>
-      <c r="D624" t="s">
-        <v>71</v>
-      </c>
-      <c r="F624" t="s">
-        <v>32</v>
-      </c>
-      <c r="G624" t="s">
-        <v>10</v>
-      </c>
-      <c r="H624" s="2">
-        <v>6.828703703703704E-3</v>
-      </c>
-      <c r="I624" s="1">
-        <v>46237.849074074074</v>
-      </c>
-      <c r="J624" s="2">
-        <v>0</v>
-      </c>
-      <c r="K624" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H624" s="2"/>
+      <c r="I624" s="1"/>
+      <c r="J624" s="2"/>
+      <c r="K624" s="1"/>
     </row>
     <row r="625" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H625" s="2"/>
@@ -25980,6 +25978,7 @@
       <c r="K1954" s="1"/>
     </row>
     <row r="1955" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1955" s="2"/>
       <c r="I1955" s="1"/>
       <c r="K1955" s="1"/>
     </row>
@@ -25989,6 +25988,7 @@
       <c r="K1956" s="1"/>
     </row>
     <row r="1957" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1957" s="2"/>
       <c r="I1957" s="1"/>
       <c r="K1957" s="1"/>
     </row>
@@ -26128,6 +26128,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -26181,7 +26182,6 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -55554,7 +55554,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -55847,8 +55846,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -56159,7 +56156,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -56284,7 +56280,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -56296,7 +56291,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -56445,35 +56439,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -56484,44 +56472,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -56532,37 +56511,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -56573,52 +56545,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -56629,17 +56591,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -56650,32 +56609,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -56685,106 +56638,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -56794,7 +56727,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -56805,127 +56737,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -56935,62 +56841,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -57010,67 +56903,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -57080,38 +56960,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -57126,117 +56999,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -57245,99 +57095,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -57347,23 +57178,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -57372,52 +57199,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -57431,38 +57248,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -57472,7 +57282,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -57483,23 +57292,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -57509,37 +57314,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -57548,72 +57346,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -57623,76 +57407,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Texas-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05BFA9D8-5A35-4265-8F11-1341A37EB300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0784DEF0-B6BA-4C30-84B9-46F30EFAD86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -146,7 +146,13 @@
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>Safe RR Crossing</t>
+    <t>DNU-Speed Management</t>
+  </si>
+  <si>
+    <t>DNU-Def.Drive Distracted Driving</t>
+  </si>
+  <si>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>3 points of contact</t>
@@ -155,16 +161,10 @@
     <t>Vehicle &amp; Roadside Inspections CMV</t>
   </si>
   <si>
-    <t>DNU-Def.Drive Distracted Driving</t>
-  </si>
-  <si>
-    <t>DNU-Speed Management</t>
+    <t>Safe RR Crossing</t>
   </si>
   <si>
     <t>DNUNEW-Space Management Big 5</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Texas Towing Wrecker Service</t>
@@ -637,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1362,7 +1362,7 @@
         <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
@@ -1391,7 +1391,7 @@
         <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
@@ -1449,7 +1449,7 @@
         <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G28" t="s">
         <v>10</v>
@@ -1478,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
@@ -1507,7 +1507,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s">
         <v>10</v>
@@ -1536,7 +1536,7 @@
         <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -1565,7 +1565,7 @@
         <v>50</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -1594,7 +1594,7 @@
         <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -1631,7 +1631,7 @@
         <v>52</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -1660,7 +1660,7 @@
         <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
@@ -1689,7 +1689,7 @@
         <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
@@ -1718,7 +1718,7 @@
         <v>55</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G38" t="s">
         <v>13</v>
@@ -1747,7 +1747,7 @@
         <v>56</v>
       </c>
       <c r="F39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G39" t="s">
         <v>14</v>
@@ -1784,7 +1784,7 @@
         <v>57</v>
       </c>
       <c r="F41" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -1821,7 +1821,7 @@
         <v>58</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G43" t="s">
         <v>10</v>
@@ -1850,7 +1850,7 @@
         <v>59</v>
       </c>
       <c r="F44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -1879,7 +1879,7 @@
         <v>60</v>
       </c>
       <c r="F45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G45" t="s">
         <v>10</v>
@@ -1908,7 +1908,7 @@
         <v>61</v>
       </c>
       <c r="F46" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G46" t="s">
         <v>10</v>
@@ -1937,7 +1937,7 @@
         <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G47" t="s">
         <v>13</v>
@@ -1966,7 +1966,7 @@
         <v>63</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
@@ -2003,7 +2003,7 @@
         <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G50" t="s">
         <v>10</v>
@@ -2032,7 +2032,7 @@
         <v>65</v>
       </c>
       <c r="F51" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>43</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -2090,7 +2090,7 @@
         <v>44</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -2119,7 +2119,7 @@
         <v>45</v>
       </c>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G54" t="s">
         <v>13</v>
@@ -2148,7 +2148,7 @@
         <v>46</v>
       </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2177,7 +2177,7 @@
         <v>47</v>
       </c>
       <c r="F56" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G56" t="s">
         <v>13</v>
@@ -2206,7 +2206,7 @@
         <v>48</v>
       </c>
       <c r="F57" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G57" t="s">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G58" t="s">
         <v>13</v>
@@ -2264,7 +2264,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
@@ -2293,7 +2293,7 @@
         <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G60" t="s">
         <v>13</v>
@@ -2322,7 +2322,7 @@
         <v>52</v>
       </c>
       <c r="F61" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
@@ -2351,7 +2351,7 @@
         <v>53</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
@@ -2380,7 +2380,7 @@
         <v>54</v>
       </c>
       <c r="F63" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G63" t="s">
         <v>13</v>
@@ -2409,7 +2409,7 @@
         <v>55</v>
       </c>
       <c r="F64" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G64" t="s">
         <v>10</v>
@@ -2438,7 +2438,7 @@
         <v>56</v>
       </c>
       <c r="F65" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G65" t="s">
         <v>10</v>
@@ -2467,7 +2467,7 @@
         <v>57</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2496,7 +2496,7 @@
         <v>58</v>
       </c>
       <c r="F67" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2525,7 +2525,7 @@
         <v>59</v>
       </c>
       <c r="F68" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G68" t="s">
         <v>13</v>
@@ -2554,7 +2554,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G69" t="s">
         <v>10</v>
@@ -2583,7 +2583,7 @@
         <v>61</v>
       </c>
       <c r="F70" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G70" t="s">
         <v>10</v>
@@ -2612,7 +2612,7 @@
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2641,7 +2641,7 @@
         <v>63</v>
       </c>
       <c r="F72" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G72" t="s">
         <v>10</v>
@@ -2670,7 +2670,7 @@
         <v>64</v>
       </c>
       <c r="F73" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2699,7 +2699,7 @@
         <v>65</v>
       </c>
       <c r="F74" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>43</v>
       </c>
       <c r="F75" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -2757,7 +2757,7 @@
         <v>44</v>
       </c>
       <c r="F76" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G76" t="s">
         <v>10</v>
@@ -2786,7 +2786,7 @@
         <v>46</v>
       </c>
       <c r="F77" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G77" t="s">
         <v>13</v>
@@ -2815,7 +2815,7 @@
         <v>47</v>
       </c>
       <c r="F78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G78" t="s">
         <v>13</v>
@@ -2844,7 +2844,7 @@
         <v>48</v>
       </c>
       <c r="F79" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G79" t="s">
         <v>10</v>
@@ -2873,7 +2873,7 @@
         <v>49</v>
       </c>
       <c r="F80" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G80" t="s">
         <v>13</v>
@@ -2902,7 +2902,7 @@
         <v>50</v>
       </c>
       <c r="F81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G81" t="s">
         <v>13</v>
@@ -2931,7 +2931,7 @@
         <v>51</v>
       </c>
       <c r="F82" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G82" t="s">
         <v>13</v>
@@ -2960,7 +2960,7 @@
         <v>52</v>
       </c>
       <c r="F83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G83" t="s">
         <v>13</v>
@@ -2989,7 +2989,7 @@
         <v>53</v>
       </c>
       <c r="F84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G84" t="s">
         <v>13</v>
@@ -3018,7 +3018,7 @@
         <v>54</v>
       </c>
       <c r="F85" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G85" t="s">
         <v>13</v>
@@ -3047,7 +3047,7 @@
         <v>55</v>
       </c>
       <c r="F86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G86" t="s">
         <v>10</v>
@@ -3076,7 +3076,7 @@
         <v>56</v>
       </c>
       <c r="F87" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G87" t="s">
         <v>14</v>
@@ -3113,7 +3113,7 @@
         <v>57</v>
       </c>
       <c r="F89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G89" t="s">
         <v>14</v>
@@ -3150,7 +3150,7 @@
         <v>58</v>
       </c>
       <c r="F91" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G91" t="s">
         <v>13</v>
@@ -3179,7 +3179,7 @@
         <v>59</v>
       </c>
       <c r="F92" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G92" t="s">
         <v>13</v>
@@ -3208,7 +3208,7 @@
         <v>60</v>
       </c>
       <c r="F93" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G93" t="s">
         <v>10</v>
@@ -3237,7 +3237,7 @@
         <v>61</v>
       </c>
       <c r="F94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G94" t="s">
         <v>12</v>
@@ -3274,7 +3274,7 @@
         <v>62</v>
       </c>
       <c r="F96" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G96" t="s">
         <v>13</v>
@@ -3303,7 +3303,7 @@
         <v>63</v>
       </c>
       <c r="F97" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G97" t="s">
         <v>13</v>
@@ -3332,7 +3332,7 @@
         <v>64</v>
       </c>
       <c r="F98" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G98" t="s">
         <v>13</v>
@@ -3361,7 +3361,7 @@
         <v>65</v>
       </c>
       <c r="F99" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G99" t="s">
         <v>10</v>
@@ -6417,7 +6417,7 @@
         <v>43</v>
       </c>
       <c r="F208" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G208" t="s">
         <v>13</v>
@@ -6446,7 +6446,7 @@
         <v>44</v>
       </c>
       <c r="F209" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G209" t="s">
         <v>10</v>
@@ -6475,7 +6475,7 @@
         <v>66</v>
       </c>
       <c r="F210" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G210" t="s">
         <v>10</v>
@@ -6504,7 +6504,7 @@
         <v>46</v>
       </c>
       <c r="F211" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G211" t="s">
         <v>13</v>
@@ -6533,7 +6533,7 @@
         <v>47</v>
       </c>
       <c r="F212" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G212" t="s">
         <v>13</v>
@@ -6562,7 +6562,7 @@
         <v>48</v>
       </c>
       <c r="F213" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G213" t="s">
         <v>10</v>
@@ -6591,7 +6591,7 @@
         <v>49</v>
       </c>
       <c r="F214" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G214" t="s">
         <v>13</v>
@@ -6620,7 +6620,7 @@
         <v>50</v>
       </c>
       <c r="F215" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G215" t="s">
         <v>13</v>
@@ -6649,7 +6649,7 @@
         <v>52</v>
       </c>
       <c r="F216" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G216" t="s">
         <v>13</v>
@@ -6678,7 +6678,7 @@
         <v>56</v>
       </c>
       <c r="F217" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G217" t="s">
         <v>14</v>
@@ -6715,7 +6715,7 @@
         <v>57</v>
       </c>
       <c r="F219" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G219" t="s">
         <v>10</v>
@@ -6744,7 +6744,7 @@
         <v>58</v>
       </c>
       <c r="F220" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G220" t="s">
         <v>13</v>
@@ -6773,7 +6773,7 @@
         <v>59</v>
       </c>
       <c r="F221" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G221" t="s">
         <v>13</v>
@@ -6802,7 +6802,7 @@
         <v>60</v>
       </c>
       <c r="F222" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G222" t="s">
         <v>10</v>
@@ -6831,7 +6831,7 @@
         <v>61</v>
       </c>
       <c r="F223" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G223" t="s">
         <v>10</v>
@@ -6860,7 +6860,7 @@
         <v>62</v>
       </c>
       <c r="F224" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G224" t="s">
         <v>13</v>
@@ -6889,7 +6889,7 @@
         <v>67</v>
       </c>
       <c r="F225" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G225" t="s">
         <v>10</v>
@@ -6918,7 +6918,7 @@
         <v>63</v>
       </c>
       <c r="F226" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G226" t="s">
         <v>10</v>
@@ -6947,7 +6947,7 @@
         <v>64</v>
       </c>
       <c r="F227" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G227" t="s">
         <v>10</v>
@@ -6976,7 +6976,7 @@
         <v>65</v>
       </c>
       <c r="F228" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G228" t="s">
         <v>10</v>
@@ -7005,7 +7005,7 @@
         <v>43</v>
       </c>
       <c r="F229" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G229" t="s">
         <v>10</v>
@@ -7034,7 +7034,7 @@
         <v>44</v>
       </c>
       <c r="F230" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G230" t="s">
         <v>10</v>
@@ -7063,7 +7063,7 @@
         <v>66</v>
       </c>
       <c r="F231" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G231" t="s">
         <v>13</v>
@@ -7092,7 +7092,7 @@
         <v>46</v>
       </c>
       <c r="F232" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G232" t="s">
         <v>13</v>
@@ -7121,7 +7121,7 @@
         <v>47</v>
       </c>
       <c r="F233" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G233" t="s">
         <v>13</v>
@@ -7150,7 +7150,7 @@
         <v>48</v>
       </c>
       <c r="F234" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G234" t="s">
         <v>10</v>
@@ -7179,7 +7179,7 @@
         <v>49</v>
       </c>
       <c r="F235" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G235" t="s">
         <v>13</v>
@@ -7208,7 +7208,7 @@
         <v>50</v>
       </c>
       <c r="F236" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G236" t="s">
         <v>13</v>
@@ -7237,7 +7237,7 @@
         <v>52</v>
       </c>
       <c r="F237" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G237" t="s">
         <v>13</v>
@@ -7266,7 +7266,7 @@
         <v>56</v>
       </c>
       <c r="F238" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G238" t="s">
         <v>14</v>
@@ -7303,7 +7303,7 @@
         <v>57</v>
       </c>
       <c r="F240" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G240" t="s">
         <v>10</v>
@@ -7332,7 +7332,7 @@
         <v>58</v>
       </c>
       <c r="F241" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G241" t="s">
         <v>13</v>
@@ -7361,7 +7361,7 @@
         <v>59</v>
       </c>
       <c r="F242" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G242" t="s">
         <v>13</v>
@@ -7390,7 +7390,7 @@
         <v>60</v>
       </c>
       <c r="F243" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G243" t="s">
         <v>13</v>
@@ -7419,7 +7419,7 @@
         <v>61</v>
       </c>
       <c r="F244" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G244" t="s">
         <v>13</v>
@@ -7448,7 +7448,7 @@
         <v>62</v>
       </c>
       <c r="F245" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G245" t="s">
         <v>13</v>
@@ -7477,7 +7477,7 @@
         <v>67</v>
       </c>
       <c r="F246" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G246" t="s">
         <v>10</v>
@@ -7506,7 +7506,7 @@
         <v>63</v>
       </c>
       <c r="F247" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G247" t="s">
         <v>10</v>
@@ -7535,7 +7535,7 @@
         <v>64</v>
       </c>
       <c r="F248" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G248" t="s">
         <v>12</v>
@@ -7572,7 +7572,7 @@
         <v>65</v>
       </c>
       <c r="F250" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G250" t="s">
         <v>10</v>
@@ -8239,7 +8239,7 @@
         <v>43</v>
       </c>
       <c r="F273" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G273" t="s">
         <v>10</v>
@@ -8268,7 +8268,7 @@
         <v>44</v>
       </c>
       <c r="F274" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G274" t="s">
         <v>10</v>
@@ -8297,7 +8297,7 @@
         <v>66</v>
       </c>
       <c r="F275" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G275" t="s">
         <v>10</v>
@@ -8326,7 +8326,7 @@
         <v>46</v>
       </c>
       <c r="F276" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G276" t="s">
         <v>10</v>
@@ -8355,7 +8355,7 @@
         <v>47</v>
       </c>
       <c r="F277" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G277" t="s">
         <v>10</v>
@@ -8384,7 +8384,7 @@
         <v>48</v>
       </c>
       <c r="F278" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G278" t="s">
         <v>10</v>
@@ -8413,7 +8413,7 @@
         <v>49</v>
       </c>
       <c r="F279" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G279" t="s">
         <v>10</v>
@@ -8442,7 +8442,7 @@
         <v>50</v>
       </c>
       <c r="F280" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G280" t="s">
         <v>13</v>
@@ -8471,7 +8471,7 @@
         <v>52</v>
       </c>
       <c r="F281" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G281" t="s">
         <v>13</v>
@@ -8500,7 +8500,7 @@
         <v>56</v>
       </c>
       <c r="F282" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G282" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>57</v>
       </c>
       <c r="F283" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G283" t="s">
         <v>10</v>
@@ -8558,7 +8558,7 @@
         <v>58</v>
       </c>
       <c r="F284" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G284" t="s">
         <v>10</v>
@@ -8587,7 +8587,7 @@
         <v>59</v>
       </c>
       <c r="F285" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G285" t="s">
         <v>10</v>
@@ -8616,7 +8616,7 @@
         <v>68</v>
       </c>
       <c r="F286" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G286" t="s">
         <v>10</v>
@@ -8645,7 +8645,7 @@
         <v>61</v>
       </c>
       <c r="F287" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G287" t="s">
         <v>10</v>
@@ -8674,7 +8674,7 @@
         <v>62</v>
       </c>
       <c r="F288" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G288" t="s">
         <v>12</v>
@@ -8711,7 +8711,7 @@
         <v>67</v>
       </c>
       <c r="F290" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G290" t="s">
         <v>10</v>
@@ -8740,7 +8740,7 @@
         <v>63</v>
       </c>
       <c r="F291" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G291" t="s">
         <v>10</v>
@@ -8769,7 +8769,7 @@
         <v>64</v>
       </c>
       <c r="F292" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G292" t="s">
         <v>10</v>
@@ -8798,7 +8798,7 @@
         <v>65</v>
       </c>
       <c r="F293" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G293" t="s">
         <v>10</v>
@@ -11804,7 +11804,7 @@
         <v>43</v>
       </c>
       <c r="F401" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G401" t="s">
         <v>10</v>
@@ -11833,7 +11833,7 @@
         <v>44</v>
       </c>
       <c r="F402" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G402" t="s">
         <v>10</v>
@@ -11862,7 +11862,7 @@
         <v>66</v>
       </c>
       <c r="F403" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G403" t="s">
         <v>10</v>
@@ -11891,7 +11891,7 @@
         <v>46</v>
       </c>
       <c r="F404" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G404" t="s">
         <v>13</v>
@@ -11920,7 +11920,7 @@
         <v>47</v>
       </c>
       <c r="F405" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G405" t="s">
         <v>13</v>
@@ -11949,7 +11949,7 @@
         <v>49</v>
       </c>
       <c r="F406" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G406" t="s">
         <v>13</v>
@@ -11978,7 +11978,7 @@
         <v>50</v>
       </c>
       <c r="F407" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G407" t="s">
         <v>13</v>
@@ -12007,7 +12007,7 @@
         <v>52</v>
       </c>
       <c r="F408" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G408" t="s">
         <v>13</v>
@@ -12036,7 +12036,7 @@
         <v>56</v>
       </c>
       <c r="F409" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G409" t="s">
         <v>10</v>
@@ -12065,7 +12065,7 @@
         <v>57</v>
       </c>
       <c r="F410" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G410" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>58</v>
       </c>
       <c r="F411" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G411" t="s">
         <v>13</v>
@@ -12123,7 +12123,7 @@
         <v>59</v>
       </c>
       <c r="F412" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G412" t="s">
         <v>12</v>
@@ -12160,7 +12160,7 @@
         <v>68</v>
       </c>
       <c r="F414" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G414" t="s">
         <v>10</v>
@@ -12189,7 +12189,7 @@
         <v>61</v>
       </c>
       <c r="F415" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G415" t="s">
         <v>10</v>
@@ -12218,7 +12218,7 @@
         <v>62</v>
       </c>
       <c r="F416" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G416" t="s">
         <v>10</v>
@@ -12247,7 +12247,7 @@
         <v>67</v>
       </c>
       <c r="F417" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G417" t="s">
         <v>10</v>
@@ -12276,7 +12276,7 @@
         <v>63</v>
       </c>
       <c r="F418" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G418" t="s">
         <v>10</v>
@@ -12305,7 +12305,7 @@
         <v>64</v>
       </c>
       <c r="F419" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G419" t="s">
         <v>10</v>
@@ -12334,7 +12334,7 @@
         <v>65</v>
       </c>
       <c r="F420" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G420" t="s">
         <v>10</v>
@@ -55554,6 +55554,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -55846,6 +55847,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -56156,6 +56159,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -56280,6 +56284,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -56291,6 +56296,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -56439,29 +56445,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -56472,35 +56484,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -56511,30 +56532,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -56545,42 +56573,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -56591,14 +56629,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -56609,26 +56650,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -56638,86 +56685,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -56727,6 +56795,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -56737,101 +56806,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -56841,49 +56936,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -56898,59 +57006,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -56960,31 +57082,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -56994,99 +57123,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -57095,80 +57248,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -57178,67 +57350,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -57248,31 +57436,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -57282,6 +57477,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -57292,19 +57488,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -57314,90 +57514,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -57407,51 +57629,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
